--- a/human_validation/judge/kor/judge_D009_S005_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S005_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 온 이유는 좀 무서운 생각들이 들어서예요. 제가 저를 다치게 하고 싶다는 건 아닌데, 그보다는... 내일 안 깨어나면 오히려 더 편하지 않을까 하는 생각이요. 결국 그것 때문에 예약을 잡게 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 생각을 하신 지 얼마나 되셨어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 걱정될 정도로 꽤 오래됐어요. 그런데 저를 정말 무섭게 한 생각은 '내일 안 깨어나면 더 편할지도 모른다'는 그런 느낌이었어요. 저를 다치게 하고 싶은 건 아닌데, 그런 생각이 든다는 것 자체가 와야겠다는 느낌을 줬어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 안 깨어나면 좋겠다는 이런 생각을 하신 지 얼마나 되셨어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 정확히 언제부터인지는 모르겠는데, 최근 들어서 무서워질 정도로 찾아오게 됐어요. 내일 안 깨어나면 더 편할지도 모른다는 그런 생각이요. 저를 다치게 하고 싶은 건 아닌데, 그런 생각이 든다는 것 자체가 힘들었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 요즘 대부분의 시간 동안 슬프거나 우울하다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 요즘 거의 매일 아침 무겁고 회색빛 같은 느낌으로 일어나요. 출근 준비를 하기도 전에 모든 게 이미 무미건조하게 느껴져요. 매 순간 계속 그런 건 아닌데, 꽤 자주 그래요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 평소에 좋아하시는 활동들을 여전히 즐기고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 사실 별로요. 물감을 꺼내놓거나 도자기 수업에 가야겠다고 생각하는 것처럼 평소에 좋아하던 걸 여전히 해보려고는 하는데, 막상 그 자리에 가면 그냥 모든 걸 멍하니 바라보게 돼요. 예전에 느끼던 그 설렘이나 흥미가 안 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 예전에 즐기시던 일들을 할 때 즐거움을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 아니요, 별로요. 그림 같은 경우에도 여전히 물감은 꺼내놓거나 도자기 수업 갈 생각은 하는데, 막상 거기 가면 그냥 재료들을 멍하니 바라보게 돼요. 예전에 느끼던 그 설렘이 안 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 최근에 체중에 뚜렷한 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 뚜렷한 변화는 딱히 못 느꼈어요. 옷도 비슷하게 맞는 것 같고, 체중도 자세히 재보진 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 요즘 잠자는 데 어려움이 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 딱히 신경 써서 살펴보지 않았는데, 수면에 큰 변화가 있었다고 딱히 눈에 띄는 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 요즘 이런저런 일들에 대해 죄책감을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네... 그래요. 보통 직장에서의 작은 일들 때문이에요. 진열 표지판이 삐뚤어져 있던 게 계속 생각나거나, 교육생이 헷갈려 하는 것 같아 보였던 게 떠올라서, 제가 쓸모없는 관리자라고 스스로 되뇌게 돼요. 균형이 안 맞는 느낌이긴 한데, 그래도 계속 거기 붙잡혀 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 요즘 안절부절못하거나 나른한 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네, 조금요. 어떤 날은 거실을 왔다 갔다 하거나 저도 모르게 손톱 거스러미를 뜯고 있는 걸 알아채요. 또 어떤 날은 좀 느려진 느낌이 들어요, 휴게실에서 매장까지 걸어가는 것도 이상하게 느리게 느껴지고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 요즘 불안하다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요. 요즘 특별히 불안하다고는 딱히 못 느꼈어요. 만약 그렇다 해도 딱히 눈에 띄지는 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 평소보다 움직임이 느려지거나 몸을 움직이는 게 힘들게 느껴지신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네. 어떤 날은 정말 느려진 느낌이 들어요, 휴게실에서 매장까지 걷는 것도 원래보다 더 힘이 드는 것 같고요. 또 어떤 날은 반대로, 저도 모르게 거실을 왔다 갔다 하거나 손톱 거스러미를 뜯고 있는 저 자신을 발견해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 안 깨어나거나 죽음에 대한 이런 생각을 자주 하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네. 계속은 아닌데, 무서울 정도로 자주요. 내일 그냥 안 깨어나면 더 편할지도 모른다는 그런 생각이 들어요. 저를 다치게 하고 싶은 건 아닌데, 그런 생각이 든다는 것 자체가 이 예약을 잡게 만들었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 이 무겁고 회색빛 같은 느낌을 거의 매일 아침 느끼신 지 몇 주 혹은 몇 달 정도 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 한 6개월 정도 된 것 같아요. 거의 매일 아침 그런 가라앉고 무미건조한 느낌이 꽤 오래 지속돼서, 미술 수업이나 아침 산책처럼 예전에 도움이 됐던 것들도 이제 별로 회복이 되는 느낌이 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 최근에 다른 사람들은 듣거나 보지 못하는 목소리나 사물을 경험하신 것처럼 특이한 지각 경험을 하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 아니요, 그런 적은 없는 것 같아요. 다른 사람들이 못 보는 걸 보거나 목소리를 들은 적은 없어요. 요즘 그런 건 전혀 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 안 깨어났으면 하는 그런 생각을 실행에 옮긴다면 어떻게 할지 구체적으로 생각해 보신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 아니요, 그런 계획을 세운 적은 없어요. 그보다는 그냥 내일 안 깨어나면 더 편할 것 같다는 생각에 가까워요. 그게 무서워서 오게 됐는데, 저를 다치게 하고 싶은 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 평소 상태보다 안절부절못하거나 나른한 느낌이 더 자주 드는 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 네, 그런 것 같아요. 어떤 날은 안절부절못해서 저도 모르게 거실을 왔다 갔다 하거나 손톱 거스러미를 뜯고요. 또 어떤 날은 반대로, 휴게실에서 매장까지 걷는 것도 더 힘이 들고 이상하게 느리게 움직이게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 본인의 생각이 자신의 것이 아니라고 느끼시거나, 누군가 혹은 무언가가 본인의 마음을 조종하고 있다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 아니요, 그런 느낌은 없었어요. 제 생각은 속상하거나 가라앉히기 힘들 때도 여전히 제 것처럼 느껴져요. 누군가 제 마음을 조종하고 있다는 느낌은 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 최근에 다른 사람들이 보기에 이상해 보일 수 있는 특이한 생각이나 믿음을 가지신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 음... 누가 저를 조종한다거나 하는 그런 이상한 건 아니에요. 근데 그렇게 에너지가 넘쳤던 시기에, 저 혼자서 매장 이미지 전체를 고칠 수 있다고 정말로 생각했어요. 제 아이디어가 훌륭하다고 확신했고, 지역 매니저가 그냥 그걸 못 알아본다고 느꼈던 게 기억나요. 돌이켜보면, 아마 현실적인 수준보다 컸던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 제1형 양극성장애 (D008); 외상후 스트레스장애 (D018) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 예전에 즐기시던 활동들에서 즐거움을 느끼지 못하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 네. 예전에 좋아하던 것들, 물감을 꺼내놓거나 도자기 수업에 가는 것처럼 여전히 해보려고 하는데, 막상 가면 그냥 재료들을 멍하니 바라보게 돼요. 예전에 느끼던 그 설렘이나 즐거움이 안 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 제1형 양극성장애 (D008); 외상후 스트레스장애 (D018) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 제2형 양극성장애 (D009)
 인구통계: 성별 여성 / 나이 62 / 직업상태 first line supervisor of retail sales worker / 최종학력 학사
@@ -575,497 +999,47 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S032
-배경 서술: 야즐린의 어려움은 새로 온 지역 매니저가 그녀의 사람 중심적인 매장 배치를 비판하고, 그녀의 유연한 멘토링 방식에 의문을 제기하고, 지역 문화 홍보 행사를 위해 그녀가 디자인한 진열을 반복적으로 뒤엎으면서 시작되었다. 그녀는 처음에는 평소답지 않게 넘치는 확신과 에너지로 반응하여, 여러 재설계안을 제안하고, 추가 교육 세션에 자원했으며, 노트를 아이디어로 가득 채웠지만 동시에 산만해지고 쉽게 딴 데로 정신이 팔렸다. 이후 2개월 동안 그 강렬함은 우울한 시기로 바뀌어, 그림 그리기, 도자기, 새벽 산책, 지역센터 사진 수업이 모두 무미건조하게 느껴졌고, 몸은 초조한 안절부절못함과 눈에 띄는 느려짐 사이를 오갔으며, 직장에서의 실수에 대해 비합리적일 정도로 무가치함을 느꼈고, 일상적인 결정을 내리는 데 어려움을 겪었으며, 실행 의도 없이 반복적으로 죽음에 대한 수동적인 생각을 경험했다. 그녀는 수년간 명상 일지를 써왔기에 이 패턴이 까다로운 상사와 함께한 힘든 한 달 이상의 무언가라는 것을 스스로 알아챘고, 직접 외래 정신건강의학과 평가 일정을 잡았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 온 이유는 좀 무서운 생각들이 들어서예요. 제가 저를 다치게 하고 싶다는 건 아닌데, 그보다는... 내일 안 깨어나면 오히려 더 편하지 않을까 하는 생각이요. 결국 그것 때문에 예약을 잡게 됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 생각을 하신 지 얼마나 되셨어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 걱정될 정도로 꽤 오래됐어요. 그런데 저를 정말 무섭게 한 생각은 '내일 안 깨어나면 더 편할지도 모른다'는 그런 느낌이었어요. 저를 다치게 하고 싶은 건 아닌데, 그런 생각이 든다는 것 자체가 와야겠다는 느낌을 줬어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 안 깨어나면 좋겠다는 이런 생각을 하신 지 얼마나 되셨어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 정확히 언제부터인지는 모르겠는데, 최근 들어서 무서워질 정도로 찾아오게 됐어요. 내일 안 깨어나면 더 편할지도 모른다는 그런 생각이요. 저를 다치게 하고 싶은 건 아닌데, 그런 생각이 든다는 것 자체가 힘들었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 요즘 대부분의 시간 동안 슬프거나 우울하다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 요즘 거의 매일 아침 무겁고 회색빛 같은 느낌으로 일어나요. 출근 준비를 하기도 전에 모든 게 이미 무미건조하게 느껴져요. 매 순간 계속 그런 건 아닌데, 꽤 자주 그래요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 평소에 좋아하시는 활동들을 여전히 즐기고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 사실 별로요. 물감을 꺼내놓거나 도자기 수업에 가야겠다고 생각하는 것처럼 평소에 좋아하던 걸 여전히 해보려고는 하는데, 막상 그 자리에 가면 그냥 모든 걸 멍하니 바라보게 돼요. 예전에 느끼던 그 설렘이나 흥미가 안 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 예전에 즐기시던 일들을 할 때 즐거움을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 아니요, 별로요. 그림 같은 경우에도 여전히 물감은 꺼내놓거나 도자기 수업 갈 생각은 하는데, 막상 거기 가면 그냥 재료들을 멍하니 바라보게 돼요. 예전에 느끼던 그 설렘이 안 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 최근에 체중에 뚜렷한 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 뚜렷한 변화는 딱히 못 느꼈어요. 옷도 비슷하게 맞는 것 같고, 체중도 자세히 재보진 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 요즘 잠자는 데 어려움이 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 딱히 신경 써서 살펴보지 않았는데, 수면에 큰 변화가 있었다고 딱히 눈에 띄는 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 요즘 이런저런 일들에 대해 죄책감을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네... 그래요. 보통 직장에서의 작은 일들 때문이에요. 진열 표지판이 삐뚤어져 있던 게 계속 생각나거나, 교육생이 헷갈려 하는 것 같아 보였던 게 떠올라서, 제가 쓸모없는 관리자라고 스스로 되뇌게 돼요. 균형이 안 맞는 느낌이긴 한데, 그래도 계속 거기 붙잡혀 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 요즘 안절부절못하거나 나른한 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네, 조금요. 어떤 날은 거실을 왔다 갔다 하거나 저도 모르게 손톱 거스러미를 뜯고 있는 걸 알아채요. 또 어떤 날은 좀 느려진 느낌이 들어요, 휴게실에서 매장까지 걸어가는 것도 이상하게 느리게 느껴지고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 요즘 불안하다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요. 요즘 특별히 불안하다고는 딱히 못 느꼈어요. 만약 그렇다 해도 딱히 눈에 띄지는 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 평소보다 움직임이 느려지거나 몸을 움직이는 게 힘들게 느껴지신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네. 어떤 날은 정말 느려진 느낌이 들어요, 휴게실에서 매장까지 걷는 것도 원래보다 더 힘이 드는 것 같고요. 또 어떤 날은 반대로, 저도 모르게 거실을 왔다 갔다 하거나 손톱 거스러미를 뜯고 있는 저 자신을 발견해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 안 깨어나거나 죽음에 대한 이런 생각을 자주 하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네. 계속은 아닌데, 무서울 정도로 자주요. 내일 그냥 안 깨어나면 더 편할지도 모른다는 그런 생각이 들어요. 저를 다치게 하고 싶은 건 아닌데, 그런 생각이 든다는 것 자체가 이 예약을 잡게 만들었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 이 무겁고 회색빛 같은 느낌을 거의 매일 아침 느끼신 지 몇 주 혹은 몇 달 정도 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 한 6개월 정도 된 것 같아요. 거의 매일 아침 그런 가라앉고 무미건조한 느낌이 꽤 오래 지속돼서, 미술 수업이나 아침 산책처럼 예전에 도움이 됐던 것들도 이제 별로 회복이 되는 느낌이 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 최근에 다른 사람들은 듣거나 보지 못하는 목소리나 사물을 경험하신 것처럼 특이한 지각 경험을 하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 아니요, 그런 적은 없는 것 같아요. 다른 사람들이 못 보는 걸 보거나 목소리를 들은 적은 없어요. 요즘 그런 건 전혀 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 안 깨어났으면 하는 그런 생각을 실행에 옮긴다면 어떻게 할지 구체적으로 생각해 보신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 아니요, 그런 계획을 세운 적은 없어요. 그보다는 그냥 내일 안 깨어나면 더 편할 것 같다는 생각에 가까워요. 그게 무서워서 오게 됐는데, 저를 다치게 하고 싶은 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 평소 상태보다 안절부절못하거나 나른한 느낌이 더 자주 드는 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 네, 그런 것 같아요. 어떤 날은 안절부절못해서 저도 모르게 거실을 왔다 갔다 하거나 손톱 거스러미를 뜯고요. 또 어떤 날은 반대로, 휴게실에서 매장까지 걷는 것도 더 힘이 들고 이상하게 느리게 움직이게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 본인의 생각이 자신의 것이 아니라고 느끼시거나, 누군가 혹은 무언가가 본인의 마음을 조종하고 있다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 아니요, 그런 느낌은 없었어요. 제 생각은 속상하거나 가라앉히기 힘들 때도 여전히 제 것처럼 느껴져요. 누군가 제 마음을 조종하고 있다는 느낌은 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 최근에 다른 사람들이 보기에 이상해 보일 수 있는 특이한 생각이나 믿음을 가지신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 음... 누가 저를 조종한다거나 하는 그런 이상한 건 아니에요. 근데 그렇게 에너지가 넘쳤던 시기에, 저 혼자서 매장 이미지 전체를 고칠 수 있다고 정말로 생각했어요. 제 아이디어가 훌륭하다고 확신했고, 지역 매니저가 그냥 그걸 못 알아본다고 느꼈던 게 기억나요. 돌이켜보면, 아마 현실적인 수준보다 컸던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 중간확률: 제1형 양극성장애 (D008); 외상후 스트레스장애 (D018) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 예전에 즐기시던 활동들에서 즐거움을 느끼지 못하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 네. 예전에 좋아하던 것들, 물감을 꺼내놓거나 도자기 수업에 가는 것처럼 여전히 해보려고 하는데, 막상 가면 그냥 재료들을 멍하니 바라보게 돼요. 예전에 느끼던 그 설렘이나 즐거움이 안 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 야즐린의 어려움은 새로 온 지역 매니저가 그녀의 사람 중심적인 매장 배치를 비판하고, 그녀의 유연한 멘토링 방식에 의문을 제기하고, 지역 문화 홍보 행사를 위해 그녀가 디자인한 진열을 반복적으로 뒤엎으면서 시작되었다. 그녀는 처음에는 평소답지 않게 넘치는 확신과 에너지로 반응하여, 여러 재설계안을 제안하고, 추가 교육 세션에 자원했으며, 노트를 아이디어로 가득 채웠지만 동시에 산만해지고 쉽게 딴 데로 정신이 팔렸다. 이후 2개월 동안 그 강렬함은 우울한 시기로 바뀌어, 그림 그리기, 도자기, 새벽 산책, 지역센터 사진 수업이 모두 무미건조하게 느껴졌고, 몸은 초조한 안절부절못함과 눈에 띄는 느려짐 사이를 오갔으며, 직장에서의 실수에 대해 비합리적일 정도로 무가치함을 느꼈고, 일상적인 결정을 내리는 데 어려움을 겪었으며, 실행 의도 없이 반복적으로 죽음에 대한 수동적인 생각을 경험했다. 그녀는 수년간 명상 일지를 써왔기에 이 패턴이 까다로운 상사와 함께한 힘든 한 달 이상의 무언가라는 것을 스스로 알아챘고, 직접 외래 정신건강의학과 평가 일정을 잡았다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S039 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 중간확률: 제1형 양극성장애 (D008); 외상후 스트레스장애 (D018) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hypomanic_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
-  누락: 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.0)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: hypomanic_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D009_S005_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S005_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1035,11 +1040,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D009_S005_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S005_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0776</v>
+        <v>0.1283</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.0776</v>
+        <v>0.1283</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
